--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487096_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487096_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6628</v>
+        <v>3.7167</v>
       </c>
       <c r="E2" t="n">
-        <v>1.574</v>
+        <v>2.4941</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0887</v>
+        <v>1.2226</v>
       </c>
       <c r="G2" t="n">
         <v>4.1655</v>
@@ -610,13 +610,13 @@
         <v>2.1231</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.4099</v>
+        <v>-0.3559</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.3087</v>
+        <v>-0.3886</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1012</v>
+        <v>0.0327</v>
       </c>
       <c r="V2" t="n">
         <v>-0.2859</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1374</v>
+        <v>2.9445</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.8253</v>
+        <v>0.0353</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9627</v>
+        <v>2.9092</v>
       </c>
       <c r="G3" t="n">
         <v>-2.7405</v>
@@ -688,13 +688,13 @@
         <v>2.7021</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.5044</v>
+        <v>-0.6973</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9386</v>
+        <v>-0.078</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5659</v>
+        <v>-0.6194</v>
       </c>
       <c r="V3" t="n">
         <v>5.6103</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. VASQUEZ BAUTISTA</t>
+          <t>M. CARRETERO GARCÍA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.876</v>
+        <v>-0.2545</v>
       </c>
       <c r="E4" t="n">
-        <v>3.1801</v>
+        <v>-0.292</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.3041</v>
+        <v>0.0375</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5889</v>
+        <v>0.0921</v>
       </c>
       <c r="H4" t="n">
-        <v>2.9684</v>
+        <v>0.4927</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6205000000000001</v>
+        <v>-0.4006</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7487</v>
+        <v>-0.295</v>
       </c>
       <c r="K4" t="n">
-        <v>2.9755</v>
+        <v>0.3726</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7733</v>
+        <v>-0.6676</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1599</v>
+        <v>0.3871</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0071</v>
+        <v>0.1201</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1528</v>
+        <v>0.267</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.1231</v>
+        <v>0.579</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.8602</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7371</v>
+        <v>0.579</v>
       </c>
       <c r="S4" t="n">
-        <v>3.5224</v>
+        <v>-0.0258</v>
       </c>
       <c r="T4" t="n">
-        <v>3.6619</v>
+        <v>0.003</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1395</v>
+        <v>-0.0288</v>
       </c>
       <c r="V4" t="n">
-        <v>-3.1122</v>
+        <v>-0.8999</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.3704</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.7418</v>
+        <v>-0.8999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. CARRETERO GARCÍA</t>
+          <t>A. VASQUEZ BAUTISTA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4805</v>
+        <v>-0.5482</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6519</v>
+        <v>0.8363</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1714</v>
+        <v>-1.3844</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0921</v>
+        <v>3.5889</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4927</v>
+        <v>2.9684</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4006</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.295</v>
+        <v>3.7487</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3726</v>
+        <v>2.9755</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6676</v>
+        <v>0.7733</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3871</v>
+        <v>-0.1599</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1201</v>
+        <v>-0.0071</v>
       </c>
       <c r="O5" t="n">
-        <v>0.267</v>
+        <v>-0.1528</v>
       </c>
       <c r="P5" t="n">
-        <v>0.579</v>
+        <v>-2.1231</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-3.8602</v>
       </c>
       <c r="R5" t="n">
-        <v>0.579</v>
+        <v>1.7371</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2518</v>
+        <v>1.0982</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3569</v>
+        <v>1.318</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1051</v>
+        <v>-0.2198</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.8999</v>
+        <v>-3.1122</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.3704</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.8999</v>
+        <v>-2.7418</v>
       </c>
     </row>
     <row r="6">
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.2336</v>
+        <v>-1.3744</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4858</v>
+        <v>0.345</v>
       </c>
       <c r="F6" t="n">
         <v>-1.7194</v>
@@ -922,10 +922,10 @@
         <v>0.386</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3265</v>
+        <v>0.1857</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4297</v>
+        <v>0.2889</v>
       </c>
       <c r="U6" t="n">
         <v>-0.1031</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.2232</v>
+        <v>-1.9635</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.3597</v>
+        <v>-2.1</v>
       </c>
       <c r="F7" t="n">
         <v>0.1365</v>
@@ -1000,10 +1000,10 @@
         <v>0.193</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3265</v>
+        <v>-0.0668</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3569</v>
+        <v>-0.09719999999999999</v>
       </c>
       <c r="U7" t="n">
         <v>0.0304</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.599</v>
+        <v>-2.8935</v>
       </c>
       <c r="E8" t="n">
         <v>0.5227000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.1217</v>
+        <v>-3.4162</v>
       </c>
       <c r="G8" t="n">
         <v>0.3639</v>
@@ -1078,13 +1078,13 @@
         <v>1.3511</v>
       </c>
       <c r="S8" t="n">
-        <v>0.07199999999999999</v>
+        <v>-0.2224</v>
       </c>
       <c r="T8" t="n">
         <v>0.3239</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2519</v>
+        <v>-0.5463</v>
       </c>
       <c r="V8" t="n">
         <v>-2.4559</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.8651</v>
+        <v>-3.9127</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.8419</v>
+        <v>-3.5415</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0232</v>
+        <v>-0.3712</v>
       </c>
       <c r="G9" t="n">
         <v>-1.7769</v>
@@ -1156,13 +1156,13 @@
         <v>1.5441</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1857</v>
+        <v>0.1381</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0132</v>
+        <v>0.3137</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1725</v>
+        <v>-0.1755</v>
       </c>
       <c r="V9" t="n">
         <v>0.0422</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. ELKSNIS</t>
+          <t>M. SOLORZANO COLSA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.3422</v>
+        <v>-4.0039</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2883</v>
+        <v>-4.3383</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.0539</v>
+        <v>0.3343</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.9156</v>
+        <v>-3.6804</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.2055</v>
+        <v>-1.3113</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2899</v>
+        <v>-2.3691</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.0275</v>
+        <v>-3.3736</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5227000000000001</v>
+        <v>-0.8903</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5048</v>
+        <v>-2.4833</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8881</v>
+        <v>-0.3068</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.6828</v>
+        <v>-0.421</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7947</v>
+        <v>0.1142</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.386</v>
+        <v>1.3511</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5441</v>
+        <v>2.3161</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5268</v>
+        <v>-0.5311</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3834</v>
+        <v>0.0004</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9102</v>
+        <v>-0.5315</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.5138</v>
+        <v>-1.1435</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.7997</v>
+        <v>-1.1435</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. SOLORZANO COLSA</t>
+          <t>R. ELKSNIS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.1927</v>
+        <v>-4.376</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.0988</v>
+        <v>-2.6701</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.094</v>
+        <v>-1.7059</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.6804</v>
+        <v>-1.9156</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.3113</v>
+        <v>-2.2055</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.3691</v>
+        <v>0.2899</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.3736</v>
+        <v>-1.0275</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.8903</v>
+        <v>-0.5227000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.4833</v>
+        <v>-0.5048</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3068</v>
+        <v>-0.8881</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.421</v>
+        <v>-1.6828</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1142</v>
+        <v>0.7947</v>
       </c>
       <c r="P11" t="n">
-        <v>1.3511</v>
+        <v>-0.386</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R11" t="n">
-        <v>2.3161</v>
+        <v>1.5441</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.7199</v>
+        <v>-0.5605</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7601</v>
+        <v>0.0017</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.9598</v>
+        <v>-0.5622</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.1435</v>
+        <v>-1.5138</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.1435</v>
+        <v>-1.7997</v>
       </c>
     </row>
     <row r="12">
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-13.2601</v>
+        <v>-12.6655</v>
       </c>
       <c r="E12" t="n">
-        <v>-9.3033</v>
+        <v>-8.708500000000001</v>
       </c>
       <c r="F12" t="n">
         <v>-3.957</v>
@@ -1363,16 +1363,16 @@
         <v>-3.909</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.5732000000000004</v>
+        <v>-0.5732000000000006</v>
       </c>
       <c r="K12" t="n">
         <v>5.210199999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>-5.783299999999999</v>
+        <v>-5.7833</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.137700000000001</v>
+        <v>-4.1377</v>
       </c>
       <c r="N12" t="n">
         <v>-6.0119</v>
@@ -1381,7 +1381,7 @@
         <v>1.8742</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.930100000000001</v>
+        <v>-1.9301</v>
       </c>
       <c r="Q12" t="n">
         <v>-16.4058</v>
@@ -1390,13 +1390,13 @@
         <v>14.4757</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.6327</v>
+        <v>-1.0378</v>
       </c>
       <c r="T12" t="n">
-        <v>1.0909</v>
+        <v>1.6858</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.7236</v>
+        <v>-2.7235</v>
       </c>
       <c r="V12" t="n">
         <v>-4.986700000000001</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. DIEYE</t>
+          <t>A. DINIS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.363200000000001</v>
+        <v>6.5686</v>
       </c>
       <c r="E13" t="n">
-        <v>4.7222</v>
+        <v>4.3582</v>
       </c>
       <c r="F13" t="n">
-        <v>3.6411</v>
+        <v>2.2104</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.2729</v>
+        <v>2.9687</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.2229</v>
+        <v>1.7699</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.05</v>
+        <v>1.1988</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.0803</v>
+        <v>2.2534</v>
       </c>
       <c r="K13" t="n">
-        <v>1.1328</v>
+        <v>2.0906</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.2131</v>
+        <v>0.1628</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.1926</v>
+        <v>0.7153</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.3557</v>
+        <v>-0.3207</v>
       </c>
       <c r="O13" t="n">
-        <v>1.1631</v>
+        <v>1.036</v>
       </c>
       <c r="P13" t="n">
-        <v>0.386</v>
+        <v>1.3511</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R13" t="n">
         <v>2.3161</v>
       </c>
       <c r="S13" t="n">
-        <v>6.2913</v>
+        <v>0.4491</v>
       </c>
       <c r="T13" t="n">
-        <v>4.7737</v>
+        <v>0.6984</v>
       </c>
       <c r="U13" t="n">
-        <v>1.5176</v>
+        <v>-0.2492</v>
       </c>
       <c r="V13" t="n">
-        <v>1.9588</v>
+        <v>1.7997</v>
       </c>
       <c r="W13" t="n">
-        <v>1.9588</v>
+        <v>2.3714</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.5717</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. DINIS</t>
+          <t>D. BARROSO VALVERDE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.5234</v>
+        <v>5.4652</v>
       </c>
       <c r="E14" t="n">
-        <v>5.2595</v>
+        <v>4.2205</v>
       </c>
       <c r="F14" t="n">
-        <v>2.264</v>
+        <v>1.2448</v>
       </c>
       <c r="G14" t="n">
-        <v>2.9687</v>
+        <v>4.0309</v>
       </c>
       <c r="H14" t="n">
-        <v>1.7699</v>
+        <v>3.7932</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1988</v>
+        <v>0.2378</v>
       </c>
       <c r="J14" t="n">
-        <v>2.2534</v>
+        <v>3.2229</v>
       </c>
       <c r="K14" t="n">
-        <v>2.0906</v>
+        <v>3.9069</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1628</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7153</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3207</v>
+        <v>-0.1137</v>
       </c>
       <c r="O14" t="n">
-        <v>1.036</v>
+        <v>0.9218</v>
       </c>
       <c r="P14" t="n">
-        <v>1.3511</v>
+        <v>0.579</v>
       </c>
       <c r="Q14" t="n">
         <v>-0.965</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3161</v>
+        <v>1.5441</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4039</v>
+        <v>0.2413</v>
       </c>
       <c r="T14" t="n">
-        <v>1.5996</v>
+        <v>0.1207</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1957</v>
+        <v>0.1206</v>
       </c>
       <c r="V14" t="n">
-        <v>1.7997</v>
+        <v>0.614</v>
       </c>
       <c r="W14" t="n">
-        <v>2.3714</v>
+        <v>1.842</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.5717</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. BARROSO VALVERDE</t>
+          <t>A. DIEYE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.3627</v>
+        <v>4.3953</v>
       </c>
       <c r="E15" t="n">
-        <v>3.5195</v>
+        <v>1.718</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8431999999999999</v>
+        <v>2.6774</v>
       </c>
       <c r="G15" t="n">
-        <v>4.0309</v>
+        <v>-0.2729</v>
       </c>
       <c r="H15" t="n">
-        <v>3.7932</v>
+        <v>-0.2229</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2378</v>
+        <v>-0.05</v>
       </c>
       <c r="J15" t="n">
-        <v>3.2229</v>
+        <v>-0.0803</v>
       </c>
       <c r="K15" t="n">
-        <v>3.9069</v>
+        <v>1.1328</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-1.2131</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8080000000000001</v>
+        <v>-0.1926</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1137</v>
+        <v>-1.3557</v>
       </c>
       <c r="O15" t="n">
-        <v>0.9218</v>
+        <v>1.1631</v>
       </c>
       <c r="P15" t="n">
-        <v>0.579</v>
+        <v>0.386</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5441</v>
+        <v>2.3161</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8613</v>
+        <v>2.3234</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5803</v>
+        <v>1.7695</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2809</v>
+        <v>0.5538999999999999</v>
       </c>
       <c r="V15" t="n">
-        <v>0.614</v>
+        <v>1.9588</v>
       </c>
       <c r="W15" t="n">
-        <v>1.842</v>
+        <v>1.9588</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.6383</v>
+        <v>3.8806</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9096</v>
+        <v>1.911</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7287</v>
+        <v>1.9696</v>
       </c>
       <c r="G16" t="n">
         <v>1.4543</v>
@@ -1702,13 +1702,13 @@
         <v>2.7021</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1019</v>
+        <v>0.1405</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4481</v>
+        <v>0.5533</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6536999999999999</v>
+        <v>-0.4128</v>
       </c>
       <c r="V16" t="n">
         <v>1.5138</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5228</v>
+        <v>0.73</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1532</v>
+        <v>-0.0531</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6761</v>
+        <v>0.7831</v>
       </c>
       <c r="G17" t="n">
         <v>0.1844</v>
@@ -1780,13 +1780,13 @@
         <v>0.965</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6266</v>
+        <v>-0.4194</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2974</v>
+        <v>-0.1973</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3292</v>
+        <v>-0.2221</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2928</v>
+        <v>-0.0122</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.226</v>
+        <v>-0.0257</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0667</v>
+        <v>0.0136</v>
       </c>
       <c r="G18" t="n">
         <v>0.5041</v>
@@ -1858,13 +1858,13 @@
         <v>0.386</v>
       </c>
       <c r="S18" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.3487</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0145</v>
+        <v>0.2148</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0535</v>
+        <v>0.1338</v>
       </c>
       <c r="V18" t="n">
         <v>-0.2859</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1303</v>
+        <v>-0.2489</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.5222</v>
+        <v>-0.7211</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3919</v>
+        <v>0.4722</v>
       </c>
       <c r="G19" t="n">
         <v>1.2208</v>
@@ -1936,13 +1936,13 @@
         <v>1.158</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.5791</v>
+        <v>-0.6977</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8923</v>
+        <v>-0.0912</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6868</v>
+        <v>-0.6065</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. RAMIREZ RUIZ</t>
+          <t>J. MORAN HUETE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7892</v>
+        <v>-1.3283</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.4818</v>
+        <v>-1.5519</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6926</v>
+        <v>0.2236</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.8729</v>
+        <v>-0.196</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.7865</v>
+        <v>-0.7058</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0864</v>
+        <v>0.5098</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.594</v>
+        <v>0.4839</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.1853</v>
+        <v>-0.1915</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.4087</v>
+        <v>0.6755</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7212</v>
+        <v>-0.68</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6012</v>
+        <v>-0.5143</v>
       </c>
       <c r="O20" t="n">
-        <v>1.3223</v>
+        <v>-0.1657</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.965</v>
+        <v>-0.386</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.8951</v>
+        <v>-1.9301</v>
       </c>
       <c r="R20" t="n">
-        <v>1.9301</v>
+        <v>1.5441</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8051</v>
+        <v>-0.7463</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6359</v>
+        <v>-0.3916</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1692</v>
+        <v>-0.3546</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2436</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.3714</v>
+        <v>0.2859</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.1278</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. MORAN HUETE</t>
+          <t>A. RAMIREZ RUIZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.177</v>
+        <v>-1.696</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0526</v>
+        <v>-2.2815</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1244</v>
+        <v>0.5855</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.196</v>
+        <v>-1.8729</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.7058</v>
+        <v>-1.7865</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5098</v>
+        <v>-0.0864</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4839</v>
+        <v>-2.594</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.1915</v>
+        <v>-1.1853</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6755</v>
+        <v>-1.4087</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.68</v>
+        <v>0.7212</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5143</v>
+        <v>-0.6012</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1657</v>
+        <v>1.3223</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.386</v>
+        <v>-0.965</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9301</v>
+        <v>-2.8951</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5441</v>
+        <v>1.9301</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.595</v>
+        <v>0.8983</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8923</v>
+        <v>0.8362000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7026</v>
+        <v>0.0621</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.2436</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2859</v>
+        <v>2.3714</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2859</v>
+        <v>-2.1278</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2586</v>
+        <v>-2.0782</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.5379</v>
+        <v>-0.4378</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.7207</v>
+        <v>-1.6404</v>
       </c>
       <c r="G22" t="n">
         <v>-1.2772</v>
@@ -2170,13 +2170,13 @@
         <v>0.965</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7185</v>
+        <v>-0.538</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5949</v>
+        <v>-0.4947</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1236</v>
+        <v>-0.0433</v>
       </c>
       <c r="V22" t="n">
         <v>-1.228</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.5023</v>
+        <v>-2.416</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.4799</v>
+        <v>-3.1795</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9776</v>
+        <v>0.7635</v>
       </c>
       <c r="G23" t="n">
         <v>-2.0332</v>
@@ -2248,13 +2248,13 @@
         <v>0.579</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4534</v>
+        <v>-0.3672</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5949</v>
+        <v>-0.2945</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1414</v>
+        <v>-0.0727</v>
       </c>
       <c r="V23" t="n">
         <v>0.3704</v>
@@ -2281,43 +2281,43 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>13.2602</v>
+        <v>13.2601</v>
       </c>
       <c r="E24" t="n">
-        <v>3.957199999999999</v>
+        <v>3.957100000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>9.303400000000002</v>
+        <v>9.3033</v>
       </c>
       <c r="G24" t="n">
         <v>4.711000000000002</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8018000000000002</v>
+        <v>0.8018000000000004</v>
       </c>
       <c r="I24" t="n">
         <v>3.909200000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>4.1378</v>
+        <v>4.137800000000001</v>
       </c>
       <c r="K24" t="n">
         <v>6.012</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.8741</v>
+        <v>-1.874100000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5731999999999999</v>
+        <v>0.5732</v>
       </c>
       <c r="N24" t="n">
-        <v>-5.210199999999999</v>
+        <v>-5.210200000000001</v>
       </c>
       <c r="O24" t="n">
         <v>5.783300000000001</v>
       </c>
       <c r="P24" t="n">
-        <v>1.930099999999999</v>
+        <v>1.9301</v>
       </c>
       <c r="Q24" t="n">
         <v>-14.4755</v>
@@ -2326,10 +2326,10 @@
         <v>16.4056</v>
       </c>
       <c r="S24" t="n">
-        <v>1.6326</v>
+        <v>1.6327</v>
       </c>
       <c r="T24" t="n">
-        <v>2.723499999999999</v>
+        <v>2.7236</v>
       </c>
       <c r="U24" t="n">
         <v>-1.0908</v>
